--- a/examples.xlsx
+++ b/examples.xlsx
@@ -5,18 +5,19 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\python\LLM_service\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\python\LLM_with_RAG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{29C1F493-F5DF-4198-BEEF-FDD3A776D43E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0BE59EA7-9800-4CAF-A483-21051293CBC2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{04117A5C-B10E-4A40-B98A-F25714476F7A}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{04117A5C-B10E-4A40-B98A-F25714476F7A}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="sql" sheetId="1" r:id="rId1"/>
+    <sheet name="医学知识" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$B$57</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">sql!$A$1:$B$57</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -39,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="114" uniqueCount="114">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="138" uniqueCount="128">
   <si>
     <t>统计技术员:张三 在2024年全年的检查患者总人次</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -1025,13 +1026,952 @@
   <si>
     <t>统计2024年6-9月，门诊MR患者的平均检查等待时间(分钟)，每个月分开统计。检查等待时间=检查时间-登记时间</t>
     <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>肝脏恶性肿瘤常见病理类型</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>经过距骨的横断面</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>人体断层解剖图谱</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>大脑</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>)</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>大脑断层解剖图谱</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>喙肱韧带的位置</t>
+  </si>
+  <si>
+    <t>判断药物作用</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>你是一个医生，请根据以下病历判断门诊处方中药物的临床作用：性别：女</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>出生日期：</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>1965</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>年</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>11</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>月</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>21</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>日</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve">  </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>年龄：</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>59</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>岁</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>就诊科别：消化内科</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve">  </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>主诉：腹部不适</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>现病史：腹部不适，嗳气，灼热感，排便可，睡眠欠佳。</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>既往史、个人史、家族史：胆道手术后</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>过敏药物：青霉素</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>流行病学史</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>无特殊</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>体格检查：腹平软，无明显压痛及反跳痛，肠鸣音正常</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>辅助检查：暂缺</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>初步诊断：胃肠神经官能症，胃食管反流，胃炎</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>处理</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>包括</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>1.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>必要的辅助检查申请；</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>2.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>治疗措施及疗程，必要时给予生活指导；</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>3.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>必要的复诊告知。</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>4.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>其他</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>：</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> {</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>门急诊检查</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>} {</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>门急诊检验</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>} {</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>门急诊治疗</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve">} </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>处方：</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> 1) (</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>集</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>7)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>氟哌噻吨美利曲辛片</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>(10.5mg*28</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>片</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>) 1.00</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>盒</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>/10.500mg qd po 2) (</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>集</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>艾普拉唑</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>(5mg*6</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>片</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>) 2.00</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>盒</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve">/5.000mg qd </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>餐前口服</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> 3) (</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>集</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>莫沙必利片</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>(5mg*36) 1.00</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>盒</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve">/5.000mg tid </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>餐前口服</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> 4) </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>铝镁加</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>(1.5g*15</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>袋</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>) 2.00</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>盒</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>/1.500g tid po</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>支气管肺发育不良诊断标准</t>
+  </si>
+  <si>
+    <t>直肠癌MRI分期</t>
+  </si>
+  <si>
+    <t>DTI对脑肿瘤诊断的价值</t>
+  </si>
+  <si>
+    <t>介绍医学伦理学的关键点</t>
+  </si>
+  <si>
+    <t>阻生牙</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>阻生牙</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Inter"/>
+        <family val="2"/>
+      </rPr>
+      <t>的定义</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>先天性胆总管囊肿</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="12">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1081,6 +2021,38 @@
       <family val="2"/>
       <charset val="134"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Inter"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="微软雅黑"/>
+      <family val="2"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Inter"/>
+      <family val="2"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Consolas"/>
+      <family val="3"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -1104,7 +2076,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1122,6 +2094,15 @@
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1458,14 +2439,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{92456AB3-A936-4D14-89D7-F0899B8D8EE6}">
   <dimension ref="A1:C57"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="30.75" customWidth="1"/>
     <col min="2" max="2" width="88.125" style="1" customWidth="1"/>
     <col min="3" max="3" width="39.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:3">
       <c r="A1" t="s">
         <v>45</v>
       </c>
@@ -1473,7 +2454,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:3">
       <c r="A2" t="s">
         <v>47</v>
       </c>
@@ -1481,7 +2462,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:3">
       <c r="A3" t="s">
         <v>48</v>
       </c>
@@ -1489,7 +2470,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:3">
       <c r="A4" t="s">
         <v>49</v>
       </c>
@@ -1497,7 +2478,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="5" spans="1:3" ht="17.25" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:3" ht="17.25">
       <c r="A5" t="s">
         <v>50</v>
       </c>
@@ -1505,7 +2486,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:3">
       <c r="A6" t="s">
         <v>51</v>
       </c>
@@ -1513,7 +2494,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="7" spans="1:3" ht="17.25" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:3" ht="17.25">
       <c r="A7" t="s">
         <v>52</v>
       </c>
@@ -1521,7 +2502,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="8" spans="1:3" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:3" ht="28.5">
       <c r="A8" t="s">
         <v>53</v>
       </c>
@@ -1529,7 +2510,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="9" spans="1:3" ht="17.25" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:3" ht="17.25">
       <c r="A9" t="s">
         <v>56</v>
       </c>
@@ -1537,7 +2518,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:3">
       <c r="A10" t="s">
         <v>55</v>
       </c>
@@ -1545,7 +2526,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="11" spans="1:3" ht="17.25" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:3" ht="17.25">
       <c r="A11" t="s">
         <v>57</v>
       </c>
@@ -1553,7 +2534,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:3">
       <c r="A12" t="s">
         <v>58</v>
       </c>
@@ -1562,7 +2543,7 @@
       </c>
       <c r="C12" s="1"/>
     </row>
-    <row r="13" spans="1:3" ht="17.25" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:3" ht="17.25">
       <c r="A13" t="s">
         <v>59</v>
       </c>
@@ -1570,7 +2551,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:3">
       <c r="A14" t="s">
         <v>60</v>
       </c>
@@ -1578,7 +2559,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:3">
       <c r="A15" t="s">
         <v>61</v>
       </c>
@@ -1586,7 +2567,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:3">
       <c r="A16" t="s">
         <v>62</v>
       </c>
@@ -1594,7 +2575,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:2">
       <c r="A17" t="s">
         <v>63</v>
       </c>
@@ -1602,7 +2583,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="18" spans="1:2" ht="17.25" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:2" ht="17.25">
       <c r="A18" t="s">
         <v>64</v>
       </c>
@@ -1610,7 +2591,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="19" spans="1:2" ht="17.25" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:2" ht="17.25">
       <c r="A19" t="s">
         <v>65</v>
       </c>
@@ -1618,7 +2599,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:2">
       <c r="A20" t="s">
         <v>66</v>
       </c>
@@ -1626,7 +2607,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="21" spans="1:2" ht="17.25" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:2" ht="17.25">
       <c r="A21" t="s">
         <v>67</v>
       </c>
@@ -1634,7 +2615,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:2">
       <c r="A22" t="s">
         <v>68</v>
       </c>
@@ -1642,7 +2623,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:2">
       <c r="A23" t="s">
         <v>69</v>
       </c>
@@ -1650,7 +2631,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="24" spans="1:2" ht="17.25" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:2" ht="17.25">
       <c r="A24" t="s">
         <v>70</v>
       </c>
@@ -1658,7 +2639,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:2">
       <c r="A25" t="s">
         <v>71</v>
       </c>
@@ -1666,7 +2647,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:2">
       <c r="A26" t="s">
         <v>72</v>
       </c>
@@ -1674,7 +2655,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:2">
       <c r="A27" t="s">
         <v>73</v>
       </c>
@@ -1682,7 +2663,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="28" spans="1:2" ht="17.25" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:2" ht="17.25">
       <c r="A28" t="s">
         <v>74</v>
       </c>
@@ -1690,7 +2671,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="29" spans="1:2" ht="17.25" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:2" ht="17.25">
       <c r="A29" t="s">
         <v>75</v>
       </c>
@@ -1698,7 +2679,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="30" spans="1:2" ht="17.25" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:2" ht="17.25">
       <c r="A30" t="s">
         <v>76</v>
       </c>
@@ -1706,7 +2687,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:2">
       <c r="A31" t="s">
         <v>77</v>
       </c>
@@ -1714,7 +2695,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:2">
       <c r="A32" t="s">
         <v>78</v>
       </c>
@@ -1722,7 +2703,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:2">
       <c r="A33" t="s">
         <v>79</v>
       </c>
@@ -1730,7 +2711,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:2">
       <c r="A34" t="s">
         <v>80</v>
       </c>
@@ -1738,7 +2719,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:2">
       <c r="A35" t="s">
         <v>81</v>
       </c>
@@ -1746,7 +2727,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="36" spans="1:2" ht="17.25" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:2" ht="17.25">
       <c r="A36" t="s">
         <v>82</v>
       </c>
@@ -1754,7 +2735,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:2">
       <c r="A37" t="s">
         <v>83</v>
       </c>
@@ -1762,7 +2743,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:2">
       <c r="A38" t="s">
         <v>84</v>
       </c>
@@ -1770,7 +2751,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:2">
       <c r="A39" t="s">
         <v>85</v>
       </c>
@@ -1778,7 +2759,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:2">
       <c r="A40" t="s">
         <v>86</v>
       </c>
@@ -1786,7 +2767,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="41" spans="1:2" ht="42.75" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:2" ht="42.75">
       <c r="A41" t="s">
         <v>87</v>
       </c>
@@ -1794,7 +2775,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="42" spans="1:2" ht="42.75" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:2" ht="42.75">
       <c r="A42" t="s">
         <v>88</v>
       </c>
@@ -1802,7 +2783,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="43" spans="1:2" ht="42.75" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:2" ht="42.75">
       <c r="A43" t="s">
         <v>89</v>
       </c>
@@ -1810,7 +2791,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="44" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:2">
       <c r="A44" t="s">
         <v>90</v>
       </c>
@@ -1818,7 +2799,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="45" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:2">
       <c r="A45" t="s">
         <v>91</v>
       </c>
@@ -1826,7 +2807,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="46" spans="1:2" ht="17.25" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:2" ht="17.25">
       <c r="A46" t="s">
         <v>92</v>
       </c>
@@ -1834,7 +2815,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="47" spans="1:2" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:2" ht="28.5">
       <c r="A47" t="s">
         <v>93</v>
       </c>
@@ -1842,7 +2823,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="48" spans="1:2" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:2" ht="28.5">
       <c r="A48" t="s">
         <v>94</v>
       </c>
@@ -1850,7 +2831,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="49" spans="1:2" ht="51.75" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:2" ht="51.75">
       <c r="A49" t="s">
         <v>95</v>
       </c>
@@ -1858,7 +2839,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="50" spans="1:2" ht="42.75" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:2" ht="42.75">
       <c r="A50" t="s">
         <v>96</v>
       </c>
@@ -1866,7 +2847,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="51" spans="1:2" ht="42.75" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:2" ht="42.75">
       <c r="A51" t="s">
         <v>97</v>
       </c>
@@ -1874,7 +2855,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="52" spans="1:2" ht="42.75" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:2" ht="42.75">
       <c r="A52" t="s">
         <v>98</v>
       </c>
@@ -1882,7 +2863,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="53" spans="1:2" ht="42.75" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:2" ht="42.75">
       <c r="A53" t="s">
         <v>99</v>
       </c>
@@ -1890,7 +2871,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="54" spans="1:2" ht="42.75" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:2" ht="42.75">
       <c r="A54" t="s">
         <v>100</v>
       </c>
@@ -1898,7 +2879,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="55" spans="1:2" ht="42.75" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:2" ht="42.75">
       <c r="A55" t="s">
         <v>101</v>
       </c>
@@ -1906,7 +2887,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="56" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:2">
       <c r="A56" t="s">
         <v>103</v>
       </c>
@@ -1914,7 +2895,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="57" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:2">
       <c r="A57" t="s">
         <v>102</v>
       </c>
@@ -1927,4 +2908,115 @@
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8FAA3361-8414-42C9-9113-AA48E58C9BE0}">
+  <dimension ref="A1:B12"/>
+  <sheetFormatPr defaultRowHeight="14.25"/>
+  <cols>
+    <col min="1" max="1" width="23.875" customWidth="1"/>
+    <col min="2" max="2" width="26.125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2">
+      <c r="A1" t="s">
+        <v>45</v>
+      </c>
+      <c r="B1" s="5" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2">
+      <c r="A2" t="s">
+        <v>114</v>
+      </c>
+      <c r="B2" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2">
+      <c r="A3" t="s">
+        <v>115</v>
+      </c>
+      <c r="B3" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" ht="16.5">
+      <c r="A4" s="8" t="s">
+        <v>117</v>
+      </c>
+      <c r="B4" s="7" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2">
+      <c r="A5" s="6" t="s">
+        <v>118</v>
+      </c>
+      <c r="B5" s="6" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" ht="16.5">
+      <c r="A6" t="s">
+        <v>119</v>
+      </c>
+      <c r="B6" s="7" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2">
+      <c r="A7" s="6" t="s">
+        <v>121</v>
+      </c>
+      <c r="B7" s="6" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2">
+      <c r="A8" s="6" t="s">
+        <v>122</v>
+      </c>
+      <c r="B8" s="6" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2">
+      <c r="A9" s="6" t="s">
+        <v>123</v>
+      </c>
+      <c r="B9" s="6" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2">
+      <c r="A10" s="6" t="s">
+        <v>124</v>
+      </c>
+      <c r="B10" s="6" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" ht="16.5">
+      <c r="A11" s="7" t="s">
+        <v>126</v>
+      </c>
+      <c r="B11" s="6" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2">
+      <c r="A12" s="6" t="s">
+        <v>127</v>
+      </c>
+      <c r="B12" s="6" t="s">
+        <v>127</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>